--- a/Projects/CmF_SHG_Women_Entrepreneurs/reports/district_analysis/Churu/excel/Churu_Survey_Analysis_Master.xlsx
+++ b/Projects/CmF_SHG_Women_Entrepreneurs/reports/district_analysis/Churu/excel/Churu_Survey_Analysis_Master.xlsx
@@ -816,13 +816,13 @@
         </is>
       </c>
       <c r="D4" s="8" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E4" s="9" t="n">
         <v>310000</v>
       </c>
       <c r="F4" s="7" t="n">
-        <v>310000</v>
+        <v>51666.66666666666</v>
       </c>
       <c r="G4" s="9" t="n">
         <v>85000</v>
@@ -881,13 +881,13 @@
         </is>
       </c>
       <c r="D5" s="8" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E5" s="9" t="n">
         <v>410000</v>
       </c>
       <c r="F5" s="7" t="n">
-        <v>410000</v>
+        <v>68333.33333333333</v>
       </c>
       <c r="G5" s="9" t="n">
         <v>80000</v>
@@ -946,13 +946,13 @@
         </is>
       </c>
       <c r="D6" s="8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E6" s="9" t="n">
         <v>410000</v>
       </c>
       <c r="F6" s="7" t="n">
-        <v>410000</v>
+        <v>82000</v>
       </c>
       <c r="G6" s="9" t="n">
         <v>80000</v>
@@ -1489,8 +1489,8 @@
           <t>Tailoring</t>
         </is>
       </c>
-      <c r="D14" s="6" t="n">
-        <v>0</v>
+      <c r="D14" s="8" t="n">
+        <v>5</v>
       </c>
       <c r="E14" s="7" t="n">
         <v>0</v>
@@ -1554,8 +1554,8 @@
           <t>Beauty parlour</t>
         </is>
       </c>
-      <c r="D15" s="6" t="n">
-        <v>0</v>
+      <c r="D15" s="8" t="n">
+        <v>1</v>
       </c>
       <c r="E15" s="7" t="n">
         <v>0</v>
@@ -1814,8 +1814,8 @@
           <t>Tent house</t>
         </is>
       </c>
-      <c r="D19" s="6" t="n">
-        <v>0</v>
+      <c r="D19" s="8" t="n">
+        <v>1</v>
       </c>
       <c r="E19" s="7" t="n">
         <v>0</v>
@@ -2228,8 +2228,8 @@
           <t>Dairy shop/Milk collection centre</t>
         </is>
       </c>
-      <c r="D25" s="6" t="n">
-        <v>0</v>
+      <c r="D25" s="8" t="n">
+        <v>1</v>
       </c>
       <c r="E25" s="7" t="n">
         <v>0</v>
@@ -2423,8 +2423,8 @@
           <t>Food making (Sweets/Namkeen/hotel)</t>
         </is>
       </c>
-      <c r="D28" s="6" t="n">
-        <v>0</v>
+      <c r="D28" s="8" t="n">
+        <v>1</v>
       </c>
       <c r="E28" s="7" t="n">
         <v>0</v>
@@ -3883,19 +3883,19 @@
         </is>
       </c>
       <c r="D5" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="E5" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" s="6" t="n">
-        <v>0</v>
+      <c r="G5" s="8" t="n">
+        <v>1</v>
       </c>
       <c r="H5" s="8" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6">
@@ -3908,8 +3908,8 @@
           <t>Fancy/Cosmetic/General store</t>
         </is>
       </c>
-      <c r="D6" s="6" t="n">
-        <v>0</v>
+      <c r="D6" s="8" t="n">
+        <v>3</v>
       </c>
       <c r="E6" s="6" t="n">
         <v>0</v>
@@ -3918,10 +3918,10 @@
         <v>0</v>
       </c>
       <c r="G6" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H6" s="8" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7">
@@ -3940,14 +3940,14 @@
       <c r="E7" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="F7" s="6" t="n">
-        <v>0</v>
+      <c r="F7" s="8" t="n">
+        <v>1</v>
       </c>
       <c r="G7" s="8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H7" s="8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8">
@@ -4156,17 +4156,17 @@
       <c r="D15" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="E15" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" s="6" t="n">
-        <v>0</v>
+      <c r="E15" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G15" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H15" s="8" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="16">
@@ -4185,14 +4185,14 @@
       <c r="E16" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="F16" s="6" t="n">
-        <v>0</v>
+      <c r="F16" s="8" t="n">
+        <v>1</v>
       </c>
       <c r="G16" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="H16" s="6" t="n">
-        <v>0</v>
+      <c r="H16" s="8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -4292,11 +4292,11 @@
       <c r="F20" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="G20" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" s="6" t="n">
-        <v>0</v>
+      <c r="G20" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H20" s="8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -4450,8 +4450,8 @@
           <t>Dairy shop/Milk collection centre</t>
         </is>
       </c>
-      <c r="D26" s="6" t="n">
-        <v>0</v>
+      <c r="D26" s="8" t="n">
+        <v>1</v>
       </c>
       <c r="E26" s="6" t="n">
         <v>0</v>
@@ -4462,8 +4462,8 @@
       <c r="G26" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="H26" s="6" t="n">
-        <v>0</v>
+      <c r="H26" s="8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -4534,14 +4534,14 @@
       <c r="E29" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="F29" s="6" t="n">
-        <v>0</v>
+      <c r="F29" s="8" t="n">
+        <v>1</v>
       </c>
       <c r="G29" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="H29" s="6" t="n">
-        <v>0</v>
+      <c r="H29" s="8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -4761,7 +4761,7 @@
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="70" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4800,11 +4800,11 @@
           <t>I need help from my family in running my enterprise more effectively</t>
         </is>
       </c>
-      <c r="C4" s="6" t="n">
-        <v>0</v>
+      <c r="C4" s="8" t="n">
+        <v>5</v>
       </c>
       <c r="D4" s="25" t="n">
-        <v>0</v>
+        <v>0.2173913043478261</v>
       </c>
     </row>
     <row r="5">
@@ -4813,11 +4813,11 @@
           <t>My husband was not supportive initially, but now helps when required</t>
         </is>
       </c>
-      <c r="C5" s="6" t="n">
-        <v>0</v>
+      <c r="C5" s="8" t="n">
+        <v>5</v>
       </c>
       <c r="D5" s="25" t="n">
-        <v>0</v>
+        <v>0.2173913043478261</v>
       </c>
     </row>
     <row r="6">
@@ -4826,11 +4826,11 @@
           <t>My husband supports/supported me financially</t>
         </is>
       </c>
-      <c r="C6" s="6" t="n">
-        <v>0</v>
+      <c r="C6" s="8" t="n">
+        <v>8</v>
       </c>
       <c r="D6" s="25" t="n">
-        <v>0</v>
+        <v>0.3478260869565217</v>
       </c>
     </row>
     <row r="7">
@@ -4840,10 +4840,10 @@
         </is>
       </c>
       <c r="C7" s="8" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D7" s="25" t="n">
-        <v>0.5</v>
+        <v>0.3478260869565217</v>
       </c>
     </row>
     <row r="8">
@@ -4852,11 +4852,11 @@
           <t>I am running my enterprise without anyone’s support</t>
         </is>
       </c>
-      <c r="C8" s="6" t="n">
-        <v>0</v>
+      <c r="C8" s="8" t="n">
+        <v>6</v>
       </c>
       <c r="D8" s="25" t="n">
-        <v>0</v>
+        <v>0.2608695652173913</v>
       </c>
     </row>
     <row r="9">
@@ -4904,11 +4904,11 @@
           <t>I travel alone and I handle negotiations independently</t>
         </is>
       </c>
-      <c r="C13" s="6" t="n">
-        <v>0</v>
+      <c r="C13" s="8" t="n">
+        <v>5</v>
       </c>
       <c r="D13" s="25" t="n">
-        <v>0</v>
+        <v>0.2173913043478261</v>
       </c>
     </row>
     <row r="14">
@@ -4917,11 +4917,11 @@
           <t>I need travel companion but I handle negotiations independently</t>
         </is>
       </c>
-      <c r="C14" s="6" t="n">
-        <v>0</v>
+      <c r="C14" s="8" t="n">
+        <v>6</v>
       </c>
       <c r="D14" s="25" t="n">
-        <v>0</v>
+        <v>0.2608695652173913</v>
       </c>
     </row>
     <row r="15">
@@ -4930,11 +4930,11 @@
           <t>My family member handles the purchase</t>
         </is>
       </c>
-      <c r="C15" s="6" t="n">
-        <v>0</v>
+      <c r="C15" s="8" t="n">
+        <v>5</v>
       </c>
       <c r="D15" s="25" t="n">
-        <v>0</v>
+        <v>0.2173913043478261</v>
       </c>
     </row>
     <row r="16">
@@ -4956,11 +4956,11 @@
           <t>I want to source material from different places but I need support</t>
         </is>
       </c>
-      <c r="C17" s="6" t="n">
-        <v>0</v>
+      <c r="C17" s="8" t="n">
+        <v>1</v>
       </c>
       <c r="D17" s="25" t="n">
-        <v>0</v>
+        <v>0.04347826086956522</v>
       </c>
     </row>
     <row r="18">
@@ -4970,10 +4970,10 @@
         </is>
       </c>
       <c r="C18" s="8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D18" s="25" t="n">
-        <v>0.5</v>
+        <v>0.2173913043478261</v>
       </c>
     </row>
     <row r="19">
@@ -5030,7 +5030,7 @@
         </is>
       </c>
       <c r="C2" s="27" t="n">
-        <v>2</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3"/>
@@ -5063,10 +5063,10 @@
         </is>
       </c>
       <c r="C5" s="8" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D5" s="25" t="n">
-        <v>1</v>
+        <v>0.5217391304347826</v>
       </c>
     </row>
     <row r="6">
@@ -5075,11 +5075,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="C6" s="6" t="n">
-        <v>0</v>
+      <c r="C6" s="8" t="n">
+        <v>11</v>
       </c>
       <c r="D6" s="25" t="n">
-        <v>0</v>
+        <v>0.4782608695652174</v>
       </c>
     </row>
     <row r="7">
@@ -5127,10 +5127,10 @@
         </is>
       </c>
       <c r="C10" s="8" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D10" s="25" t="n">
-        <v>0.5</v>
+        <v>0.2608695652173913</v>
       </c>
     </row>
     <row r="11">
@@ -5140,10 +5140,10 @@
         </is>
       </c>
       <c r="C11" s="8" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="D11" s="25" t="n">
-        <v>0.5</v>
+        <v>0.7391304347826086</v>
       </c>
     </row>
     <row r="12">
@@ -5191,10 +5191,10 @@
         </is>
       </c>
       <c r="C15" s="8" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="D15" s="25" t="n">
-        <v>1</v>
+        <v>0.6521739130434783</v>
       </c>
     </row>
     <row r="16">
@@ -5204,10 +5204,10 @@
         </is>
       </c>
       <c r="C16" s="8" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D16" s="25" t="n">
-        <v>0.5</v>
+        <v>0.3478260869565217</v>
       </c>
     </row>
     <row r="17">
@@ -5216,11 +5216,11 @@
           <t>In Production</t>
         </is>
       </c>
-      <c r="C17" s="6" t="n">
-        <v>0</v>
+      <c r="C17" s="8" t="n">
+        <v>2</v>
       </c>
       <c r="D17" s="25" t="n">
-        <v>0</v>
+        <v>0.08695652173913043</v>
       </c>
     </row>
     <row r="18">
@@ -5268,10 +5268,10 @@
         </is>
       </c>
       <c r="C21" s="8" t="n">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="D21" s="25" t="n">
-        <v>1</v>
+        <v>0.9565217391304348</v>
       </c>
     </row>
     <row r="22">
@@ -5281,7 +5281,7 @@
         </is>
       </c>
       <c r="C22" s="8" t="n">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="D22" s="25" t="n">
         <v>1</v>
@@ -5294,10 +5294,10 @@
         </is>
       </c>
       <c r="C23" s="8" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="D23" s="25" t="n">
-        <v>0.5</v>
+        <v>0.6086956521739131</v>
       </c>
     </row>
     <row r="24">
@@ -5306,11 +5306,11 @@
           <t>Shop and Establishment registration</t>
         </is>
       </c>
-      <c r="C24" s="6" t="n">
-        <v>0</v>
+      <c r="C24" s="8" t="n">
+        <v>2</v>
       </c>
       <c r="D24" s="25" t="n">
-        <v>0</v>
+        <v>0.08695652173913043</v>
       </c>
     </row>
     <row r="25">
@@ -5333,10 +5333,10 @@
         </is>
       </c>
       <c r="C26" s="8" t="n">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="D26" s="25" t="n">
-        <v>1</v>
+        <v>0.9565217391304348</v>
       </c>
     </row>
     <row r="27">
@@ -5345,11 +5345,11 @@
           <t>Income certificate</t>
         </is>
       </c>
-      <c r="C27" s="6" t="n">
-        <v>0</v>
+      <c r="C27" s="8" t="n">
+        <v>10</v>
       </c>
       <c r="D27" s="25" t="n">
-        <v>0</v>
+        <v>0.4347826086956522</v>
       </c>
     </row>
     <row r="28">
@@ -5409,11 +5409,11 @@
           <t>26-35</t>
         </is>
       </c>
-      <c r="C32" s="6" t="n">
-        <v>0</v>
+      <c r="C32" s="8" t="n">
+        <v>8</v>
       </c>
       <c r="D32" s="25" t="n">
-        <v>0</v>
+        <v>0.3478260869565217</v>
       </c>
     </row>
     <row r="33">
@@ -5423,10 +5423,10 @@
         </is>
       </c>
       <c r="C33" s="8" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D33" s="25" t="n">
-        <v>0.5</v>
+        <v>0.3478260869565217</v>
       </c>
     </row>
     <row r="34">
@@ -5436,10 +5436,10 @@
         </is>
       </c>
       <c r="C34" s="8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D34" s="25" t="n">
-        <v>0.5</v>
+        <v>0.2173913043478261</v>
       </c>
     </row>
     <row r="35">
@@ -5448,11 +5448,11 @@
           <t>Above 55</t>
         </is>
       </c>
-      <c r="C35" s="6" t="n">
-        <v>0</v>
+      <c r="C35" s="8" t="n">
+        <v>2</v>
       </c>
       <c r="D35" s="25" t="n">
-        <v>0</v>
+        <v>0.08695652173913043</v>
       </c>
     </row>
     <row r="36">
@@ -5513,10 +5513,10 @@
         </is>
       </c>
       <c r="C40" s="8" t="n">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="D40" s="25" t="n">
-        <v>1</v>
+        <v>0.9565217391304348</v>
       </c>
     </row>
     <row r="41">
@@ -5525,11 +5525,11 @@
           <t>Widowed</t>
         </is>
       </c>
-      <c r="C41" s="6" t="n">
-        <v>0</v>
+      <c r="C41" s="8" t="n">
+        <v>1</v>
       </c>
       <c r="D41" s="25" t="n">
-        <v>0</v>
+        <v>0.04347826086956522</v>
       </c>
     </row>
     <row r="42">
@@ -5603,10 +5603,10 @@
         </is>
       </c>
       <c r="C47" s="8" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D47" s="25" t="n">
-        <v>0.5</v>
+        <v>0.3478260869565217</v>
       </c>
     </row>
     <row r="48">
@@ -5615,11 +5615,11 @@
           <t>ST</t>
         </is>
       </c>
-      <c r="C48" s="6" t="n">
-        <v>0</v>
+      <c r="C48" s="8" t="n">
+        <v>1</v>
       </c>
       <c r="D48" s="25" t="n">
-        <v>0</v>
+        <v>0.04347826086956522</v>
       </c>
     </row>
     <row r="49">
@@ -5628,11 +5628,11 @@
           <t>OBC</t>
         </is>
       </c>
-      <c r="C49" s="6" t="n">
-        <v>0</v>
+      <c r="C49" s="8" t="n">
+        <v>6</v>
       </c>
       <c r="D49" s="25" t="n">
-        <v>0</v>
+        <v>0.2608695652173913</v>
       </c>
     </row>
     <row r="50">
@@ -5642,10 +5642,10 @@
         </is>
       </c>
       <c r="C50" s="8" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D50" s="25" t="n">
-        <v>0.5</v>
+        <v>0.3478260869565217</v>
       </c>
     </row>
     <row r="51">
@@ -5692,11 +5692,11 @@
           <t>Illiterate</t>
         </is>
       </c>
-      <c r="C54" s="6" t="n">
-        <v>0</v>
+      <c r="C54" s="8" t="n">
+        <v>3</v>
       </c>
       <c r="D54" s="25" t="n">
-        <v>0</v>
+        <v>0.1304347826086956</v>
       </c>
     </row>
     <row r="55">
@@ -5719,10 +5719,10 @@
         </is>
       </c>
       <c r="C56" s="8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D56" s="25" t="n">
-        <v>0.5</v>
+        <v>0.2173913043478261</v>
       </c>
     </row>
     <row r="57">
@@ -5732,10 +5732,10 @@
         </is>
       </c>
       <c r="C57" s="8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D57" s="25" t="n">
-        <v>0.5</v>
+        <v>0.1739130434782609</v>
       </c>
     </row>
     <row r="58">
@@ -5744,11 +5744,11 @@
           <t>Upto 10th</t>
         </is>
       </c>
-      <c r="C58" s="6" t="n">
-        <v>0</v>
+      <c r="C58" s="8" t="n">
+        <v>2</v>
       </c>
       <c r="D58" s="25" t="n">
-        <v>0</v>
+        <v>0.08695652173913043</v>
       </c>
     </row>
     <row r="59">
@@ -5757,11 +5757,11 @@
           <t>Upto 12th</t>
         </is>
       </c>
-      <c r="C59" s="6" t="n">
-        <v>0</v>
+      <c r="C59" s="8" t="n">
+        <v>3</v>
       </c>
       <c r="D59" s="25" t="n">
-        <v>0</v>
+        <v>0.1304347826086956</v>
       </c>
     </row>
     <row r="60">
@@ -5783,11 +5783,11 @@
           <t>Graduate</t>
         </is>
       </c>
-      <c r="C61" s="6" t="n">
-        <v>0</v>
+      <c r="C61" s="8" t="n">
+        <v>5</v>
       </c>
       <c r="D61" s="25" t="n">
-        <v>0</v>
+        <v>0.2173913043478261</v>
       </c>
     </row>
     <row r="62">
@@ -5796,11 +5796,11 @@
           <t>B.Ed</t>
         </is>
       </c>
-      <c r="C62" s="6" t="n">
-        <v>0</v>
+      <c r="C62" s="8" t="n">
+        <v>1</v>
       </c>
       <c r="D62" s="25" t="n">
-        <v>0</v>
+        <v>0.04347826086956522</v>
       </c>
     </row>
     <row r="63">
@@ -5848,10 +5848,10 @@
         </is>
       </c>
       <c r="C66" s="8" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D66" s="25" t="n">
-        <v>0.5</v>
+        <v>0.4347826086956522</v>
       </c>
     </row>
     <row r="67">
@@ -5861,10 +5861,10 @@
         </is>
       </c>
       <c r="C67" s="8" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D67" s="25" t="n">
-        <v>0.5</v>
+        <v>0.4782608695652174</v>
       </c>
     </row>
     <row r="68">
@@ -5873,11 +5873,11 @@
           <t>6-8</t>
         </is>
       </c>
-      <c r="C68" s="6" t="n">
-        <v>0</v>
+      <c r="C68" s="8" t="n">
+        <v>1</v>
       </c>
       <c r="D68" s="25" t="n">
-        <v>0</v>
+        <v>0.04347826086956522</v>
       </c>
     </row>
     <row r="69">
@@ -5899,11 +5899,11 @@
           <t>More than 10</t>
         </is>
       </c>
-      <c r="C70" s="6" t="n">
-        <v>0</v>
+      <c r="C70" s="8" t="n">
+        <v>1</v>
       </c>
       <c r="D70" s="25" t="n">
-        <v>0</v>
+        <v>0.04347826086956522</v>
       </c>
     </row>
     <row r="71">
@@ -5967,7 +5967,7 @@
         <v>1</v>
       </c>
       <c r="D75" s="25" t="n">
-        <v>0.5</v>
+        <v>0.04347826086956522</v>
       </c>
     </row>
     <row r="76">
@@ -5980,7 +5980,7 @@
         <v>1</v>
       </c>
       <c r="D76" s="25" t="n">
-        <v>0.5</v>
+        <v>0.04347826086956522</v>
       </c>
     </row>
     <row r="77">
@@ -6092,11 +6092,11 @@
           <t>Rs 80,000 to Rs 1,20,000</t>
         </is>
       </c>
-      <c r="C85" s="6" t="n">
-        <v>0</v>
+      <c r="C85" s="8" t="n">
+        <v>1</v>
       </c>
       <c r="D85" s="25" t="n">
-        <v>0</v>
+        <v>0.04347826086956522</v>
       </c>
     </row>
     <row r="86">
@@ -6105,11 +6105,11 @@
           <t>Rs 1,20,001 to Rs 1,60,000</t>
         </is>
       </c>
-      <c r="C86" s="6" t="n">
-        <v>0</v>
+      <c r="C86" s="8" t="n">
+        <v>2</v>
       </c>
       <c r="D86" s="25" t="n">
-        <v>0</v>
+        <v>0.08695652173913043</v>
       </c>
     </row>
     <row r="87">
@@ -6118,11 +6118,11 @@
           <t>Rs 1,60,001 to Rs 2,00,000</t>
         </is>
       </c>
-      <c r="C87" s="6" t="n">
-        <v>0</v>
+      <c r="C87" s="8" t="n">
+        <v>3</v>
       </c>
       <c r="D87" s="25" t="n">
-        <v>0</v>
+        <v>0.1304347826086956</v>
       </c>
     </row>
     <row r="88">
@@ -6131,11 +6131,11 @@
           <t>Rs 2,00,001 to Rs 2,40,000</t>
         </is>
       </c>
-      <c r="C88" s="6" t="n">
-        <v>0</v>
+      <c r="C88" s="8" t="n">
+        <v>3</v>
       </c>
       <c r="D88" s="25" t="n">
-        <v>0</v>
+        <v>0.1304347826086956</v>
       </c>
     </row>
     <row r="89">
@@ -6171,10 +6171,10 @@
         </is>
       </c>
       <c r="C91" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D91" s="25" t="n">
-        <v>0.5</v>
+        <v>0.1304347826086956</v>
       </c>
     </row>
     <row r="92">
@@ -6184,10 +6184,10 @@
         </is>
       </c>
       <c r="C92" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D92" s="25" t="n">
-        <v>0.5</v>
+        <v>0.1304347826086956</v>
       </c>
     </row>
     <row r="93">
@@ -6196,11 +6196,11 @@
           <t>Above Rs 4,00,001</t>
         </is>
       </c>
-      <c r="C93" s="6" t="n">
-        <v>0</v>
+      <c r="C93" s="8" t="n">
+        <v>8</v>
       </c>
       <c r="D93" s="25" t="n">
-        <v>0</v>
+        <v>0.3478260869565217</v>
       </c>
     </row>
     <row r="94">
@@ -6251,7 +6251,7 @@
         <v>2</v>
       </c>
       <c r="D97" s="25" t="n">
-        <v>1</v>
+        <v>0.08695652173913043</v>
       </c>
     </row>
     <row r="98">
@@ -6264,7 +6264,7 @@
         <v>1</v>
       </c>
       <c r="D98" s="25" t="n">
-        <v>0.5</v>
+        <v>0.04347826086956522</v>
       </c>
     </row>
     <row r="99">
@@ -6277,7 +6277,7 @@
         <v>2</v>
       </c>
       <c r="D99" s="25" t="n">
-        <v>1</v>
+        <v>0.08695652173913043</v>
       </c>
     </row>
     <row r="100">
@@ -6342,7 +6342,7 @@
         <v>2</v>
       </c>
       <c r="D104" s="25" t="n">
-        <v>1</v>
+        <v>0.08695652173913043</v>
       </c>
     </row>
     <row r="105">
@@ -6355,7 +6355,7 @@
         <v>2</v>
       </c>
       <c r="D105" s="25" t="n">
-        <v>1</v>
+        <v>0.08695652173913043</v>
       </c>
     </row>
     <row r="106">
@@ -6407,7 +6407,7 @@
         <v>1</v>
       </c>
       <c r="D109" s="25" t="n">
-        <v>0.5</v>
+        <v>0.04347826086956522</v>
       </c>
     </row>
     <row r="110">
@@ -6471,7 +6471,7 @@
         <v>2</v>
       </c>
       <c r="D114" s="25" t="n">
-        <v>1</v>
+        <v>0.08695652173913043</v>
       </c>
     </row>
     <row r="115">
@@ -6497,7 +6497,7 @@
         <v>1</v>
       </c>
       <c r="D116" s="25" t="n">
-        <v>0.5</v>
+        <v>0.04347826086956522</v>
       </c>
     </row>
     <row r="117">
@@ -6601,7 +6601,7 @@
         <v>1</v>
       </c>
       <c r="D124" s="25" t="n">
-        <v>0.5</v>
+        <v>0.04347826086956522</v>
       </c>
     </row>
     <row r="125">
@@ -6648,11 +6648,11 @@
           <t>SHG loan is sufficient for the current scale of my business</t>
         </is>
       </c>
-      <c r="C128" s="6" t="n">
-        <v>0</v>
+      <c r="C128" s="8" t="n">
+        <v>7</v>
       </c>
       <c r="D128" s="25" t="n">
-        <v>0</v>
+        <v>0.3043478260869565</v>
       </c>
     </row>
     <row r="129">
@@ -6662,10 +6662,10 @@
         </is>
       </c>
       <c r="C129" s="8" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="D129" s="25" t="n">
-        <v>1</v>
+        <v>0.5652173913043478</v>
       </c>
     </row>
     <row r="130">
@@ -6675,10 +6675,10 @@
         </is>
       </c>
       <c r="C130" s="8" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D130" s="25" t="n">
-        <v>1</v>
+        <v>0.4347826086956522</v>
       </c>
     </row>
     <row r="131">
@@ -6700,11 +6700,11 @@
           <t>My family members help me with funds and loans</t>
         </is>
       </c>
-      <c r="C132" s="6" t="n">
-        <v>0</v>
+      <c r="C132" s="8" t="n">
+        <v>1</v>
       </c>
       <c r="D132" s="25" t="n">
-        <v>0</v>
+        <v>0.04347826086956522</v>
       </c>
     </row>
     <row r="133">
@@ -6726,11 +6726,11 @@
           <t>I don't prefer money lender or NBFIs as the repayment time is shorter for my convenience</t>
         </is>
       </c>
-      <c r="C134" s="6" t="n">
-        <v>0</v>
+      <c r="C134" s="8" t="n">
+        <v>1</v>
       </c>
       <c r="D134" s="25" t="n">
-        <v>0</v>
+        <v>0.04347826086956522</v>
       </c>
     </row>
     <row r="135">
@@ -6781,7 +6781,7 @@
         <v>1</v>
       </c>
       <c r="D138" s="25" t="n">
-        <v>0.5</v>
+        <v>0.04347826086956522</v>
       </c>
     </row>
     <row r="139">
@@ -6794,7 +6794,7 @@
         <v>2</v>
       </c>
       <c r="D139" s="25" t="n">
-        <v>1</v>
+        <v>0.08695652173913043</v>
       </c>
     </row>
     <row r="140">
@@ -6807,7 +6807,7 @@
         <v>2</v>
       </c>
       <c r="D140" s="25" t="n">
-        <v>1</v>
+        <v>0.08695652173913043</v>
       </c>
     </row>
     <row r="141">
@@ -6820,7 +6820,7 @@
         <v>1</v>
       </c>
       <c r="D141" s="25" t="n">
-        <v>0.5</v>
+        <v>0.04347826086956522</v>
       </c>
     </row>
     <row r="142">
@@ -6833,7 +6833,7 @@
         <v>1</v>
       </c>
       <c r="D142" s="25" t="n">
-        <v>0.5</v>
+        <v>0.04347826086956522</v>
       </c>
     </row>
     <row r="143">
@@ -6846,7 +6846,7 @@
         <v>1</v>
       </c>
       <c r="D143" s="25" t="n">
-        <v>0.5</v>
+        <v>0.04347826086956522</v>
       </c>
     </row>
     <row r="144">
@@ -6859,7 +6859,7 @@
         <v>1</v>
       </c>
       <c r="D144" s="25" t="n">
-        <v>0.5</v>
+        <v>0.04347826086956522</v>
       </c>
     </row>
     <row r="145">
@@ -6907,10 +6907,10 @@
         </is>
       </c>
       <c r="C148" s="8" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="D148" s="25" t="n">
-        <v>0.5</v>
+        <v>0.5652173913043478</v>
       </c>
     </row>
     <row r="149">
@@ -6919,11 +6919,11 @@
           <t>Rs 1,00,001-Rs 3,00,000</t>
         </is>
       </c>
-      <c r="C149" s="6" t="n">
-        <v>0</v>
+      <c r="C149" s="8" t="n">
+        <v>6</v>
       </c>
       <c r="D149" s="25" t="n">
-        <v>0</v>
+        <v>0.2608695652173913</v>
       </c>
     </row>
     <row r="150">
@@ -6932,11 +6932,11 @@
           <t>Rs 3,00,001-Rs 5,00,000</t>
         </is>
       </c>
-      <c r="C150" s="6" t="n">
-        <v>0</v>
+      <c r="C150" s="8" t="n">
+        <v>2</v>
       </c>
       <c r="D150" s="25" t="n">
-        <v>0</v>
+        <v>0.08695652173913043</v>
       </c>
     </row>
     <row r="151">
@@ -6945,11 +6945,11 @@
           <t>Rs 5,00,001-Rs 7,00,000</t>
         </is>
       </c>
-      <c r="C151" s="6" t="n">
-        <v>0</v>
+      <c r="C151" s="8" t="n">
+        <v>1</v>
       </c>
       <c r="D151" s="25" t="n">
-        <v>0</v>
+        <v>0.04347826086956522</v>
       </c>
     </row>
     <row r="152">
@@ -7022,11 +7022,11 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="C157" s="6" t="n">
-        <v>0</v>
+      <c r="C157" s="8" t="n">
+        <v>1</v>
       </c>
       <c r="D157" s="25" t="n">
-        <v>0</v>
+        <v>0.04347826086956522</v>
       </c>
     </row>
     <row r="158">
@@ -7036,10 +7036,10 @@
         </is>
       </c>
       <c r="C158" s="8" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="D158" s="25" t="n">
-        <v>0.5</v>
+        <v>0.9130434782608695</v>
       </c>
     </row>
     <row r="159">
@@ -7086,11 +7086,11 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="C162" s="6" t="n">
-        <v>0</v>
+      <c r="C162" s="8" t="n">
+        <v>1</v>
       </c>
       <c r="D162" s="25" t="n">
-        <v>0</v>
+        <v>0.04347826086956522</v>
       </c>
     </row>
     <row r="163">
@@ -7189,11 +7189,11 @@
           <t>Rs 4000 to Rs 5000</t>
         </is>
       </c>
-      <c r="C170" s="6" t="n">
-        <v>0</v>
+      <c r="C170" s="8" t="n">
+        <v>1</v>
       </c>
       <c r="D170" s="25" t="n">
-        <v>0</v>
+        <v>0.04347826086956522</v>
       </c>
     </row>
     <row r="171">
@@ -7216,10 +7216,10 @@
         </is>
       </c>
       <c r="C172" s="8" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="D172" s="25" t="n">
-        <v>0.5</v>
+        <v>0.8695652173913043</v>
       </c>
     </row>
     <row r="173">
@@ -7228,11 +7228,11 @@
           <t>Cant say</t>
         </is>
       </c>
-      <c r="C173" s="6" t="n">
-        <v>0</v>
+      <c r="C173" s="8" t="n">
+        <v>1</v>
       </c>
       <c r="D173" s="25" t="n">
-        <v>0</v>
+        <v>0.04347826086956522</v>
       </c>
     </row>
     <row r="174">
@@ -7293,10 +7293,10 @@
         </is>
       </c>
       <c r="C178" s="8" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="D178" s="25" t="n">
-        <v>0.5</v>
+        <v>0.6086956521739131</v>
       </c>
     </row>
     <row r="179">
@@ -7305,11 +7305,11 @@
           <t>They helped us to understand business plans</t>
         </is>
       </c>
-      <c r="C179" s="6" t="n">
-        <v>0</v>
+      <c r="C179" s="8" t="n">
+        <v>13</v>
       </c>
       <c r="D179" s="25" t="n">
-        <v>0</v>
+        <v>0.5652173913043478</v>
       </c>
     </row>
     <row r="180">
@@ -7318,11 +7318,11 @@
           <t>They gave us new ideas to improve our profit.</t>
         </is>
       </c>
-      <c r="C180" s="6" t="n">
-        <v>0</v>
+      <c r="C180" s="8" t="n">
+        <v>13</v>
       </c>
       <c r="D180" s="25" t="n">
-        <v>0</v>
+        <v>0.5652173913043478</v>
       </c>
     </row>
     <row r="181">
@@ -7331,11 +7331,11 @@
           <t>They trained us on maintaining records which we didn’t know earlier</t>
         </is>
       </c>
-      <c r="C181" s="6" t="n">
-        <v>0</v>
+      <c r="C181" s="8" t="n">
+        <v>3</v>
       </c>
       <c r="D181" s="25" t="n">
-        <v>0</v>
+        <v>0.1304347826086956</v>
       </c>
     </row>
     <row r="182">
@@ -7357,11 +7357,11 @@
           <t>They helped in our communication skills</t>
         </is>
       </c>
-      <c r="C183" s="6" t="n">
-        <v>0</v>
+      <c r="C183" s="8" t="n">
+        <v>9</v>
       </c>
       <c r="D183" s="25" t="n">
-        <v>0</v>
+        <v>0.391304347826087</v>
       </c>
     </row>
     <row r="184">
@@ -7370,11 +7370,11 @@
           <t>They helped in marketing</t>
         </is>
       </c>
-      <c r="C184" s="6" t="n">
-        <v>0</v>
+      <c r="C184" s="8" t="n">
+        <v>3</v>
       </c>
       <c r="D184" s="25" t="n">
-        <v>0</v>
+        <v>0.1304347826086956</v>
       </c>
     </row>
     <row r="185">
@@ -7396,11 +7396,11 @@
           <t>They helped us to understand our competitors and suggested ways to beat the competition</t>
         </is>
       </c>
-      <c r="C186" s="6" t="n">
-        <v>0</v>
+      <c r="C186" s="8" t="n">
+        <v>1</v>
       </c>
       <c r="D186" s="25" t="n">
-        <v>0</v>
+        <v>0.04347826086956522</v>
       </c>
     </row>
     <row r="187">
@@ -7448,10 +7448,10 @@
         </is>
       </c>
       <c r="C190" s="8" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="D190" s="25" t="n">
-        <v>0.5</v>
+        <v>0.8260869565217391</v>
       </c>
     </row>
     <row r="191">
@@ -7460,11 +7460,11 @@
           <t>Need help in accessing Mudra loan</t>
         </is>
       </c>
-      <c r="C191" s="6" t="n">
-        <v>0</v>
+      <c r="C191" s="8" t="n">
+        <v>2</v>
       </c>
       <c r="D191" s="25" t="n">
-        <v>0</v>
+        <v>0.08695652173913043</v>
       </c>
     </row>
     <row r="192">
@@ -7474,10 +7474,10 @@
         </is>
       </c>
       <c r="C192" s="8" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D192" s="25" t="n">
-        <v>0.5</v>
+        <v>0.3478260869565217</v>
       </c>
     </row>
     <row r="193">
@@ -7486,11 +7486,11 @@
           <t>Need help to access bigger markets</t>
         </is>
       </c>
-      <c r="C193" s="6" t="n">
-        <v>0</v>
+      <c r="C193" s="8" t="n">
+        <v>5</v>
       </c>
       <c r="D193" s="25" t="n">
-        <v>0</v>
+        <v>0.2173913043478261</v>
       </c>
     </row>
     <row r="194">
@@ -7512,11 +7512,11 @@
           <t>Need help with instagram</t>
         </is>
       </c>
-      <c r="C195" s="6" t="n">
-        <v>0</v>
+      <c r="C195" s="8" t="n">
+        <v>1</v>
       </c>
       <c r="D195" s="25" t="n">
-        <v>0</v>
+        <v>0.04347826086956522</v>
       </c>
     </row>
     <row r="196">
@@ -7538,11 +7538,11 @@
           <t>Any other, Specify</t>
         </is>
       </c>
-      <c r="C197" s="6" t="n">
-        <v>0</v>
+      <c r="C197" s="8" t="n">
+        <v>2</v>
       </c>
       <c r="D197" s="25" t="n">
-        <v>0</v>
+        <v>0.08695652173913043</v>
       </c>
     </row>
     <row r="198">
@@ -7589,11 +7589,11 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="C201" s="6" t="n">
-        <v>0</v>
+      <c r="C201" s="8" t="n">
+        <v>13</v>
       </c>
       <c r="D201" s="25" t="n">
-        <v>0</v>
+        <v>0.5652173913043478</v>
       </c>
     </row>
     <row r="202">
@@ -7603,10 +7603,10 @@
         </is>
       </c>
       <c r="C202" s="8" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D202" s="25" t="n">
-        <v>0.5</v>
+        <v>0.3478260869565217</v>
       </c>
     </row>
     <row r="203">
@@ -7615,11 +7615,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="C203" s="6" t="n">
-        <v>0</v>
+      <c r="C203" s="8" t="n">
+        <v>1</v>
       </c>
       <c r="D203" s="25" t="n">
-        <v>0</v>
+        <v>0.04347826086956522</v>
       </c>
     </row>
     <row r="204">
@@ -7667,10 +7667,10 @@
         </is>
       </c>
       <c r="C207" s="8" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="D207" s="25" t="n">
-        <v>0.5</v>
+        <v>0.7391304347826086</v>
       </c>
     </row>
     <row r="208">
@@ -7679,11 +7679,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="C208" s="6" t="n">
-        <v>0</v>
+      <c r="C208" s="8" t="n">
+        <v>5</v>
       </c>
       <c r="D208" s="25" t="n">
-        <v>0</v>
+        <v>0.2173913043478261</v>
       </c>
     </row>
     <row r="209">
@@ -7730,11 +7730,11 @@
           <t>1-4</t>
         </is>
       </c>
-      <c r="C212" s="6" t="n">
-        <v>0</v>
+      <c r="C212" s="8" t="n">
+        <v>2</v>
       </c>
       <c r="D212" s="25" t="n">
-        <v>0</v>
+        <v>0.08695652173913043</v>
       </c>
     </row>
     <row r="213">
@@ -7744,10 +7744,10 @@
         </is>
       </c>
       <c r="C213" s="8" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D213" s="25" t="n">
-        <v>0.5</v>
+        <v>0.391304347826087</v>
       </c>
     </row>
     <row r="214">
@@ -7756,11 +7756,11 @@
           <t>10-20</t>
         </is>
       </c>
-      <c r="C214" s="6" t="n">
-        <v>0</v>
+      <c r="C214" s="8" t="n">
+        <v>3</v>
       </c>
       <c r="D214" s="25" t="n">
-        <v>0</v>
+        <v>0.1304347826086956</v>
       </c>
     </row>
     <row r="215">
@@ -7769,11 +7769,11 @@
           <t>20-40</t>
         </is>
       </c>
-      <c r="C215" s="6" t="n">
-        <v>0</v>
+      <c r="C215" s="8" t="n">
+        <v>1</v>
       </c>
       <c r="D215" s="25" t="n">
-        <v>0</v>
+        <v>0.04347826086956522</v>
       </c>
     </row>
     <row r="216">
@@ -7782,11 +7782,11 @@
           <t>More than 40</t>
         </is>
       </c>
-      <c r="C216" s="6" t="n">
-        <v>0</v>
+      <c r="C216" s="8" t="n">
+        <v>2</v>
       </c>
       <c r="D216" s="25" t="n">
-        <v>0</v>
+        <v>0.08695652173913043</v>
       </c>
     </row>
     <row r="217">
@@ -7833,11 +7833,11 @@
           <t>I regularly share images on whatsapp to get orders</t>
         </is>
       </c>
-      <c r="C220" s="6" t="n">
-        <v>0</v>
+      <c r="C220" s="8" t="n">
+        <v>7</v>
       </c>
       <c r="D220" s="25" t="n">
-        <v>0</v>
+        <v>0.3043478260869565</v>
       </c>
     </row>
     <row r="221">
@@ -7859,11 +7859,11 @@
           <t>It is important but I don’t have access to smart phone</t>
         </is>
       </c>
-      <c r="C222" s="6" t="n">
-        <v>0</v>
+      <c r="C222" s="8" t="n">
+        <v>1</v>
       </c>
       <c r="D222" s="25" t="n">
-        <v>0</v>
+        <v>0.04347826086956522</v>
       </c>
     </row>
     <row r="223">
@@ -7899,10 +7899,10 @@
         </is>
       </c>
       <c r="C225" s="8" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D225" s="25" t="n">
-        <v>0.5</v>
+        <v>0.391304347826087</v>
       </c>
     </row>
     <row r="226">
@@ -7911,11 +7911,11 @@
           <t>Any other, specify</t>
         </is>
       </c>
-      <c r="C226" s="6" t="n">
-        <v>0</v>
+      <c r="C226" s="8" t="n">
+        <v>5</v>
       </c>
       <c r="D226" s="25" t="n">
-        <v>0</v>
+        <v>0.2173913043478261</v>
       </c>
     </row>
     <row r="227">
@@ -7962,11 +7962,11 @@
           <t>Whatsapp</t>
         </is>
       </c>
-      <c r="C230" s="6" t="n">
-        <v>0</v>
+      <c r="C230" s="8" t="n">
+        <v>7</v>
       </c>
       <c r="D230" s="25" t="n">
-        <v>0</v>
+        <v>0.3043478260869565</v>
       </c>
     </row>
     <row r="231">
@@ -7975,11 +7975,11 @@
           <t>Instagram</t>
         </is>
       </c>
-      <c r="C231" s="6" t="n">
-        <v>0</v>
+      <c r="C231" s="8" t="n">
+        <v>2</v>
       </c>
       <c r="D231" s="25" t="n">
-        <v>0</v>
+        <v>0.08695652173913043</v>
       </c>
     </row>
     <row r="232">
@@ -8001,11 +8001,11 @@
           <t>Facebook</t>
         </is>
       </c>
-      <c r="C233" s="6" t="n">
-        <v>0</v>
+      <c r="C233" s="8" t="n">
+        <v>1</v>
       </c>
       <c r="D233" s="25" t="n">
-        <v>0</v>
+        <v>0.04347826086956522</v>
       </c>
     </row>
     <row r="234">
@@ -8028,10 +8028,10 @@
         </is>
       </c>
       <c r="C235" s="8" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="D235" s="25" t="n">
-        <v>0.5</v>
+        <v>0.6956521739130435</v>
       </c>
     </row>
     <row r="236">
@@ -8078,11 +8078,11 @@
           <t>Use texts to ask/share prices and book orders</t>
         </is>
       </c>
-      <c r="C239" s="6" t="n">
-        <v>0</v>
+      <c r="C239" s="8" t="n">
+        <v>4</v>
       </c>
       <c r="D239" s="25" t="n">
-        <v>0</v>
+        <v>0.1739130434782609</v>
       </c>
     </row>
     <row r="240">
@@ -8091,11 +8091,11 @@
           <t>Share images to promote business</t>
         </is>
       </c>
-      <c r="C240" s="6" t="n">
-        <v>0</v>
+      <c r="C240" s="8" t="n">
+        <v>3</v>
       </c>
       <c r="D240" s="25" t="n">
-        <v>0</v>
+        <v>0.1304347826086956</v>
       </c>
     </row>
     <row r="241">
@@ -8178,7 +8178,7 @@
       </c>
       <c r="C247" s="32" t="inlineStr">
         <is>
-          <t>5.5 Years</t>
+          <t>4.7 Years</t>
         </is>
       </c>
     </row>
@@ -8190,7 +8190,7 @@
       </c>
       <c r="C248" s="32" t="inlineStr">
         <is>
-          <t>2.5 Years</t>
+          <t>3.6 Years</t>
         </is>
       </c>
     </row>
@@ -8202,7 +8202,7 @@
       </c>
       <c r="C249" s="32" t="inlineStr">
         <is>
-          <t>5.5 Years</t>
+          <t>5.1 Years</t>
         </is>
       </c>
     </row>

--- a/Projects/CmF_SHG_Women_Entrepreneurs/reports/district_analysis/Churu/excel/Churu_Survey_Analysis_Master.xlsx
+++ b/Projects/CmF_SHG_Women_Entrepreneurs/reports/district_analysis/Churu/excel/Churu_Survey_Analysis_Master.xlsx
@@ -816,13 +816,13 @@
         </is>
       </c>
       <c r="D4" s="8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E4" s="9" t="n">
         <v>310000</v>
       </c>
       <c r="F4" s="7" t="n">
-        <v>51666.66666666666</v>
+        <v>62000</v>
       </c>
       <c r="G4" s="9" t="n">
         <v>85000</v>
@@ -946,22 +946,22 @@
         </is>
       </c>
       <c r="D6" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="E6" s="9" t="n">
-        <v>410000</v>
+        <v>4</v>
+      </c>
+      <c r="E6" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="F6" s="7" t="n">
-        <v>82000</v>
-      </c>
-      <c r="G6" s="9" t="n">
-        <v>80000</v>
+        <v>0</v>
+      </c>
+      <c r="G6" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="H6" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="I6" s="9" t="n">
-        <v>200000</v>
+      <c r="I6" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="J6" s="7" t="n">
         <v>0</v>
@@ -975,11 +975,11 @@
       <c r="M6" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="N6" s="9" t="n">
-        <v>90000</v>
-      </c>
-      <c r="O6" s="9" t="n">
-        <v>40000</v>
+      <c r="N6" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="P6" s="7" t="n">
         <v>0</v>
@@ -996,8 +996,8 @@
       <c r="T6" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="U6" s="8" t="n">
-        <v>1</v>
+      <c r="U6" s="6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -1490,7 +1490,7 @@
         </is>
       </c>
       <c r="D14" s="8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E14" s="7" t="n">
         <v>0</v>
@@ -3891,11 +3891,11 @@
       <c r="F5" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="G5" s="8" t="n">
-        <v>1</v>
+      <c r="G5" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="H5" s="8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
@@ -3944,10 +3944,10 @@
         <v>1</v>
       </c>
       <c r="G7" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="H7" s="8" t="n">
         <v>4</v>
-      </c>
-      <c r="H7" s="8" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="8">
@@ -4163,10 +4163,10 @@
         <v>2</v>
       </c>
       <c r="G15" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H15" s="8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16">

--- a/Projects/CmF_SHG_Women_Entrepreneurs/reports/district_analysis/Churu/excel/Churu_Survey_Analysis_Master.xlsx
+++ b/Projects/CmF_SHG_Women_Entrepreneurs/reports/district_analysis/Churu/excel/Churu_Survey_Analysis_Master.xlsx
@@ -881,13 +881,13 @@
         </is>
       </c>
       <c r="D5" s="8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E5" s="9" t="n">
         <v>410000</v>
       </c>
       <c r="F5" s="7" t="n">
-        <v>68333.33333333333</v>
+        <v>58571.42857142857</v>
       </c>
       <c r="G5" s="9" t="n">
         <v>80000</v>
@@ -3914,14 +3914,14 @@
       <c r="E6" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="F6" s="6" t="n">
-        <v>0</v>
+      <c r="F6" s="8" t="n">
+        <v>1</v>
       </c>
       <c r="G6" s="8" t="n">
         <v>3</v>
       </c>
       <c r="H6" s="8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7">
@@ -4804,7 +4804,7 @@
         <v>5</v>
       </c>
       <c r="D4" s="25" t="n">
-        <v>0.2173913043478261</v>
+        <v>0.2083333333333333</v>
       </c>
     </row>
     <row r="5">
@@ -4817,7 +4817,7 @@
         <v>5</v>
       </c>
       <c r="D5" s="25" t="n">
-        <v>0.2173913043478261</v>
+        <v>0.2083333333333333</v>
       </c>
     </row>
     <row r="6">
@@ -4830,7 +4830,7 @@
         <v>8</v>
       </c>
       <c r="D6" s="25" t="n">
-        <v>0.3478260869565217</v>
+        <v>0.3333333333333333</v>
       </c>
     </row>
     <row r="7">
@@ -4840,10 +4840,10 @@
         </is>
       </c>
       <c r="C7" s="8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D7" s="25" t="n">
-        <v>0.3478260869565217</v>
+        <v>0.375</v>
       </c>
     </row>
     <row r="8">
@@ -4856,7 +4856,7 @@
         <v>6</v>
       </c>
       <c r="D8" s="25" t="n">
-        <v>0.2608695652173913</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="9">
@@ -4908,7 +4908,7 @@
         <v>5</v>
       </c>
       <c r="D13" s="25" t="n">
-        <v>0.2173913043478261</v>
+        <v>0.2083333333333333</v>
       </c>
     </row>
     <row r="14">
@@ -4921,7 +4921,7 @@
         <v>6</v>
       </c>
       <c r="D14" s="25" t="n">
-        <v>0.2608695652173913</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="15">
@@ -4931,10 +4931,10 @@
         </is>
       </c>
       <c r="C15" s="8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D15" s="25" t="n">
-        <v>0.2173913043478261</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="16">
@@ -4960,7 +4960,7 @@
         <v>1</v>
       </c>
       <c r="D17" s="25" t="n">
-        <v>0.04347826086956522</v>
+        <v>0.04166666666666666</v>
       </c>
     </row>
     <row r="18">
@@ -4973,7 +4973,7 @@
         <v>5</v>
       </c>
       <c r="D18" s="25" t="n">
-        <v>0.2173913043478261</v>
+        <v>0.2083333333333333</v>
       </c>
     </row>
     <row r="19">
@@ -5030,7 +5030,7 @@
         </is>
       </c>
       <c r="C2" s="27" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3"/>
@@ -5066,7 +5066,7 @@
         <v>12</v>
       </c>
       <c r="D5" s="25" t="n">
-        <v>0.5217391304347826</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="6">
@@ -5076,10 +5076,10 @@
         </is>
       </c>
       <c r="C6" s="8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D6" s="25" t="n">
-        <v>0.4782608695652174</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="7">
@@ -5130,7 +5130,7 @@
         <v>6</v>
       </c>
       <c r="D10" s="25" t="n">
-        <v>0.2608695652173913</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="11">
@@ -5140,10 +5140,10 @@
         </is>
       </c>
       <c r="C11" s="8" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D11" s="25" t="n">
-        <v>0.7391304347826086</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="12">
@@ -5191,10 +5191,10 @@
         </is>
       </c>
       <c r="C15" s="8" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D15" s="25" t="n">
-        <v>0.6521739130434783</v>
+        <v>0.6666666666666666</v>
       </c>
     </row>
     <row r="16">
@@ -5207,7 +5207,7 @@
         <v>8</v>
       </c>
       <c r="D16" s="25" t="n">
-        <v>0.3478260869565217</v>
+        <v>0.3333333333333333</v>
       </c>
     </row>
     <row r="17">
@@ -5220,7 +5220,7 @@
         <v>2</v>
       </c>
       <c r="D17" s="25" t="n">
-        <v>0.08695652173913043</v>
+        <v>0.08333333333333333</v>
       </c>
     </row>
     <row r="18">
@@ -5268,10 +5268,10 @@
         </is>
       </c>
       <c r="C21" s="8" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D21" s="25" t="n">
-        <v>0.9565217391304348</v>
+        <v>0.9583333333333334</v>
       </c>
     </row>
     <row r="22">
@@ -5281,7 +5281,7 @@
         </is>
       </c>
       <c r="C22" s="8" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D22" s="25" t="n">
         <v>1</v>
@@ -5294,10 +5294,10 @@
         </is>
       </c>
       <c r="C23" s="8" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D23" s="25" t="n">
-        <v>0.6086956521739131</v>
+        <v>0.625</v>
       </c>
     </row>
     <row r="24">
@@ -5310,7 +5310,7 @@
         <v>2</v>
       </c>
       <c r="D24" s="25" t="n">
-        <v>0.08695652173913043</v>
+        <v>0.08333333333333333</v>
       </c>
     </row>
     <row r="25">
@@ -5333,10 +5333,10 @@
         </is>
       </c>
       <c r="C26" s="8" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D26" s="25" t="n">
-        <v>0.9565217391304348</v>
+        <v>0.9583333333333334</v>
       </c>
     </row>
     <row r="27">
@@ -5346,10 +5346,10 @@
         </is>
       </c>
       <c r="C27" s="8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D27" s="25" t="n">
-        <v>0.4347826086956522</v>
+        <v>0.4583333333333333</v>
       </c>
     </row>
     <row r="28">
@@ -5413,7 +5413,7 @@
         <v>8</v>
       </c>
       <c r="D32" s="25" t="n">
-        <v>0.3478260869565217</v>
+        <v>0.3333333333333333</v>
       </c>
     </row>
     <row r="33">
@@ -5423,10 +5423,10 @@
         </is>
       </c>
       <c r="C33" s="8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D33" s="25" t="n">
-        <v>0.3478260869565217</v>
+        <v>0.375</v>
       </c>
     </row>
     <row r="34">
@@ -5439,7 +5439,7 @@
         <v>5</v>
       </c>
       <c r="D34" s="25" t="n">
-        <v>0.2173913043478261</v>
+        <v>0.2083333333333333</v>
       </c>
     </row>
     <row r="35">
@@ -5452,7 +5452,7 @@
         <v>2</v>
       </c>
       <c r="D35" s="25" t="n">
-        <v>0.08695652173913043</v>
+        <v>0.08333333333333333</v>
       </c>
     </row>
     <row r="36">
@@ -5513,10 +5513,10 @@
         </is>
       </c>
       <c r="C40" s="8" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D40" s="25" t="n">
-        <v>0.9565217391304348</v>
+        <v>0.9583333333333334</v>
       </c>
     </row>
     <row r="41">
@@ -5529,7 +5529,7 @@
         <v>1</v>
       </c>
       <c r="D41" s="25" t="n">
-        <v>0.04347826086956522</v>
+        <v>0.04166666666666666</v>
       </c>
     </row>
     <row r="42">
@@ -5606,7 +5606,7 @@
         <v>8</v>
       </c>
       <c r="D47" s="25" t="n">
-        <v>0.3478260869565217</v>
+        <v>0.3333333333333333</v>
       </c>
     </row>
     <row r="48">
@@ -5619,7 +5619,7 @@
         <v>1</v>
       </c>
       <c r="D48" s="25" t="n">
-        <v>0.04347826086956522</v>
+        <v>0.04166666666666666</v>
       </c>
     </row>
     <row r="49">
@@ -5629,10 +5629,10 @@
         </is>
       </c>
       <c r="C49" s="8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D49" s="25" t="n">
-        <v>0.2608695652173913</v>
+        <v>0.2916666666666667</v>
       </c>
     </row>
     <row r="50">
@@ -5645,7 +5645,7 @@
         <v>8</v>
       </c>
       <c r="D50" s="25" t="n">
-        <v>0.3478260869565217</v>
+        <v>0.3333333333333333</v>
       </c>
     </row>
     <row r="51">
@@ -5696,7 +5696,7 @@
         <v>3</v>
       </c>
       <c r="D54" s="25" t="n">
-        <v>0.1304347826086956</v>
+        <v>0.125</v>
       </c>
     </row>
     <row r="55">
@@ -5722,7 +5722,7 @@
         <v>5</v>
       </c>
       <c r="D56" s="25" t="n">
-        <v>0.2173913043478261</v>
+        <v>0.2083333333333333</v>
       </c>
     </row>
     <row r="57">
@@ -5735,7 +5735,7 @@
         <v>4</v>
       </c>
       <c r="D57" s="25" t="n">
-        <v>0.1739130434782609</v>
+        <v>0.1666666666666667</v>
       </c>
     </row>
     <row r="58">
@@ -5745,10 +5745,10 @@
         </is>
       </c>
       <c r="C58" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D58" s="25" t="n">
-        <v>0.08695652173913043</v>
+        <v>0.125</v>
       </c>
     </row>
     <row r="59">
@@ -5761,7 +5761,7 @@
         <v>3</v>
       </c>
       <c r="D59" s="25" t="n">
-        <v>0.1304347826086956</v>
+        <v>0.125</v>
       </c>
     </row>
     <row r="60">
@@ -5787,7 +5787,7 @@
         <v>5</v>
       </c>
       <c r="D61" s="25" t="n">
-        <v>0.2173913043478261</v>
+        <v>0.2083333333333333</v>
       </c>
     </row>
     <row r="62">
@@ -5800,7 +5800,7 @@
         <v>1</v>
       </c>
       <c r="D62" s="25" t="n">
-        <v>0.04347826086956522</v>
+        <v>0.04166666666666666</v>
       </c>
     </row>
     <row r="63">
@@ -5851,7 +5851,7 @@
         <v>10</v>
       </c>
       <c r="D66" s="25" t="n">
-        <v>0.4347826086956522</v>
+        <v>0.4166666666666667</v>
       </c>
     </row>
     <row r="67">
@@ -5861,10 +5861,10 @@
         </is>
       </c>
       <c r="C67" s="8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D67" s="25" t="n">
-        <v>0.4782608695652174</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="68">
@@ -5877,7 +5877,7 @@
         <v>1</v>
       </c>
       <c r="D68" s="25" t="n">
-        <v>0.04347826086956522</v>
+        <v>0.04166666666666666</v>
       </c>
     </row>
     <row r="69">
@@ -5903,7 +5903,7 @@
         <v>1</v>
       </c>
       <c r="D70" s="25" t="n">
-        <v>0.04347826086956522</v>
+        <v>0.04166666666666666</v>
       </c>
     </row>
     <row r="71">
@@ -5967,7 +5967,7 @@
         <v>1</v>
       </c>
       <c r="D75" s="25" t="n">
-        <v>0.04347826086956522</v>
+        <v>0.04166666666666666</v>
       </c>
     </row>
     <row r="76">
@@ -5980,7 +5980,7 @@
         <v>1</v>
       </c>
       <c r="D76" s="25" t="n">
-        <v>0.04347826086956522</v>
+        <v>0.04166666666666666</v>
       </c>
     </row>
     <row r="77">
@@ -6096,7 +6096,7 @@
         <v>1</v>
       </c>
       <c r="D85" s="25" t="n">
-        <v>0.04347826086956522</v>
+        <v>0.04166666666666666</v>
       </c>
     </row>
     <row r="86">
@@ -6109,7 +6109,7 @@
         <v>2</v>
       </c>
       <c r="D86" s="25" t="n">
-        <v>0.08695652173913043</v>
+        <v>0.08333333333333333</v>
       </c>
     </row>
     <row r="87">
@@ -6122,7 +6122,7 @@
         <v>3</v>
       </c>
       <c r="D87" s="25" t="n">
-        <v>0.1304347826086956</v>
+        <v>0.125</v>
       </c>
     </row>
     <row r="88">
@@ -6135,7 +6135,7 @@
         <v>3</v>
       </c>
       <c r="D88" s="25" t="n">
-        <v>0.1304347826086956</v>
+        <v>0.125</v>
       </c>
     </row>
     <row r="89">
@@ -6174,7 +6174,7 @@
         <v>3</v>
       </c>
       <c r="D91" s="25" t="n">
-        <v>0.1304347826086956</v>
+        <v>0.125</v>
       </c>
     </row>
     <row r="92">
@@ -6187,7 +6187,7 @@
         <v>3</v>
       </c>
       <c r="D92" s="25" t="n">
-        <v>0.1304347826086956</v>
+        <v>0.125</v>
       </c>
     </row>
     <row r="93">
@@ -6197,10 +6197,10 @@
         </is>
       </c>
       <c r="C93" s="8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D93" s="25" t="n">
-        <v>0.3478260869565217</v>
+        <v>0.375</v>
       </c>
     </row>
     <row r="94">
@@ -6251,7 +6251,7 @@
         <v>2</v>
       </c>
       <c r="D97" s="25" t="n">
-        <v>0.08695652173913043</v>
+        <v>0.08333333333333333</v>
       </c>
     </row>
     <row r="98">
@@ -6264,7 +6264,7 @@
         <v>1</v>
       </c>
       <c r="D98" s="25" t="n">
-        <v>0.04347826086956522</v>
+        <v>0.04166666666666666</v>
       </c>
     </row>
     <row r="99">
@@ -6277,7 +6277,7 @@
         <v>2</v>
       </c>
       <c r="D99" s="25" t="n">
-        <v>0.08695652173913043</v>
+        <v>0.08333333333333333</v>
       </c>
     </row>
     <row r="100">
@@ -6342,7 +6342,7 @@
         <v>2</v>
       </c>
       <c r="D104" s="25" t="n">
-        <v>0.08695652173913043</v>
+        <v>0.08333333333333333</v>
       </c>
     </row>
     <row r="105">
@@ -6355,7 +6355,7 @@
         <v>2</v>
       </c>
       <c r="D105" s="25" t="n">
-        <v>0.08695652173913043</v>
+        <v>0.08333333333333333</v>
       </c>
     </row>
     <row r="106">
@@ -6407,7 +6407,7 @@
         <v>1</v>
       </c>
       <c r="D109" s="25" t="n">
-        <v>0.04347826086956522</v>
+        <v>0.04166666666666666</v>
       </c>
     </row>
     <row r="110">
@@ -6471,7 +6471,7 @@
         <v>2</v>
       </c>
       <c r="D114" s="25" t="n">
-        <v>0.08695652173913043</v>
+        <v>0.08333333333333333</v>
       </c>
     </row>
     <row r="115">
@@ -6497,7 +6497,7 @@
         <v>1</v>
       </c>
       <c r="D116" s="25" t="n">
-        <v>0.04347826086956522</v>
+        <v>0.04166666666666666</v>
       </c>
     </row>
     <row r="117">
@@ -6601,7 +6601,7 @@
         <v>1</v>
       </c>
       <c r="D124" s="25" t="n">
-        <v>0.04347826086956522</v>
+        <v>0.04166666666666666</v>
       </c>
     </row>
     <row r="125">
@@ -6649,10 +6649,10 @@
         </is>
       </c>
       <c r="C128" s="8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D128" s="25" t="n">
-        <v>0.3043478260869565</v>
+        <v>0.3333333333333333</v>
       </c>
     </row>
     <row r="129">
@@ -6662,10 +6662,10 @@
         </is>
       </c>
       <c r="C129" s="8" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D129" s="25" t="n">
-        <v>0.5652173913043478</v>
+        <v>0.5833333333333334</v>
       </c>
     </row>
     <row r="130">
@@ -6678,7 +6678,7 @@
         <v>10</v>
       </c>
       <c r="D130" s="25" t="n">
-        <v>0.4347826086956522</v>
+        <v>0.4166666666666667</v>
       </c>
     </row>
     <row r="131">
@@ -6704,7 +6704,7 @@
         <v>1</v>
       </c>
       <c r="D132" s="25" t="n">
-        <v>0.04347826086956522</v>
+        <v>0.04166666666666666</v>
       </c>
     </row>
     <row r="133">
@@ -6730,7 +6730,7 @@
         <v>1</v>
       </c>
       <c r="D134" s="25" t="n">
-        <v>0.04347826086956522</v>
+        <v>0.04166666666666666</v>
       </c>
     </row>
     <row r="135">
@@ -6781,7 +6781,7 @@
         <v>1</v>
       </c>
       <c r="D138" s="25" t="n">
-        <v>0.04347826086956522</v>
+        <v>0.04166666666666666</v>
       </c>
     </row>
     <row r="139">
@@ -6794,7 +6794,7 @@
         <v>2</v>
       </c>
       <c r="D139" s="25" t="n">
-        <v>0.08695652173913043</v>
+        <v>0.08333333333333333</v>
       </c>
     </row>
     <row r="140">
@@ -6807,7 +6807,7 @@
         <v>2</v>
       </c>
       <c r="D140" s="25" t="n">
-        <v>0.08695652173913043</v>
+        <v>0.08333333333333333</v>
       </c>
     </row>
     <row r="141">
@@ -6820,7 +6820,7 @@
         <v>1</v>
       </c>
       <c r="D141" s="25" t="n">
-        <v>0.04347826086956522</v>
+        <v>0.04166666666666666</v>
       </c>
     </row>
     <row r="142">
@@ -6833,7 +6833,7 @@
         <v>1</v>
       </c>
       <c r="D142" s="25" t="n">
-        <v>0.04347826086956522</v>
+        <v>0.04166666666666666</v>
       </c>
     </row>
     <row r="143">
@@ -6846,7 +6846,7 @@
         <v>1</v>
       </c>
       <c r="D143" s="25" t="n">
-        <v>0.04347826086956522</v>
+        <v>0.04166666666666666</v>
       </c>
     </row>
     <row r="144">
@@ -6859,7 +6859,7 @@
         <v>1</v>
       </c>
       <c r="D144" s="25" t="n">
-        <v>0.04347826086956522</v>
+        <v>0.04166666666666666</v>
       </c>
     </row>
     <row r="145">
@@ -6910,7 +6910,7 @@
         <v>13</v>
       </c>
       <c r="D148" s="25" t="n">
-        <v>0.5652173913043478</v>
+        <v>0.5416666666666666</v>
       </c>
     </row>
     <row r="149">
@@ -6923,7 +6923,7 @@
         <v>6</v>
       </c>
       <c r="D149" s="25" t="n">
-        <v>0.2608695652173913</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="150">
@@ -6936,7 +6936,7 @@
         <v>2</v>
       </c>
       <c r="D150" s="25" t="n">
-        <v>0.08695652173913043</v>
+        <v>0.08333333333333333</v>
       </c>
     </row>
     <row r="151">
@@ -6946,10 +6946,10 @@
         </is>
       </c>
       <c r="C151" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D151" s="25" t="n">
-        <v>0.04347826086956522</v>
+        <v>0.08333333333333333</v>
       </c>
     </row>
     <row r="152">
@@ -7026,7 +7026,7 @@
         <v>1</v>
       </c>
       <c r="D157" s="25" t="n">
-        <v>0.04347826086956522</v>
+        <v>0.04166666666666666</v>
       </c>
     </row>
     <row r="158">
@@ -7036,10 +7036,10 @@
         </is>
       </c>
       <c r="C158" s="8" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D158" s="25" t="n">
-        <v>0.9130434782608695</v>
+        <v>0.9166666666666666</v>
       </c>
     </row>
     <row r="159">
@@ -7090,7 +7090,7 @@
         <v>1</v>
       </c>
       <c r="D162" s="25" t="n">
-        <v>0.04347826086956522</v>
+        <v>0.04166666666666666</v>
       </c>
     </row>
     <row r="163">
@@ -7193,7 +7193,7 @@
         <v>1</v>
       </c>
       <c r="D170" s="25" t="n">
-        <v>0.04347826086956522</v>
+        <v>0.04166666666666666</v>
       </c>
     </row>
     <row r="171">
@@ -7216,10 +7216,10 @@
         </is>
       </c>
       <c r="C172" s="8" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D172" s="25" t="n">
-        <v>0.8695652173913043</v>
+        <v>0.875</v>
       </c>
     </row>
     <row r="173">
@@ -7232,7 +7232,7 @@
         <v>1</v>
       </c>
       <c r="D173" s="25" t="n">
-        <v>0.04347826086956522</v>
+        <v>0.04166666666666666</v>
       </c>
     </row>
     <row r="174">
@@ -7293,10 +7293,10 @@
         </is>
       </c>
       <c r="C178" s="8" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D178" s="25" t="n">
-        <v>0.6086956521739131</v>
+        <v>0.625</v>
       </c>
     </row>
     <row r="179">
@@ -7309,7 +7309,7 @@
         <v>13</v>
       </c>
       <c r="D179" s="25" t="n">
-        <v>0.5652173913043478</v>
+        <v>0.5416666666666666</v>
       </c>
     </row>
     <row r="180">
@@ -7322,7 +7322,7 @@
         <v>13</v>
       </c>
       <c r="D180" s="25" t="n">
-        <v>0.5652173913043478</v>
+        <v>0.5416666666666666</v>
       </c>
     </row>
     <row r="181">
@@ -7335,7 +7335,7 @@
         <v>3</v>
       </c>
       <c r="D181" s="25" t="n">
-        <v>0.1304347826086956</v>
+        <v>0.125</v>
       </c>
     </row>
     <row r="182">
@@ -7361,7 +7361,7 @@
         <v>9</v>
       </c>
       <c r="D183" s="25" t="n">
-        <v>0.391304347826087</v>
+        <v>0.375</v>
       </c>
     </row>
     <row r="184">
@@ -7374,7 +7374,7 @@
         <v>3</v>
       </c>
       <c r="D184" s="25" t="n">
-        <v>0.1304347826086956</v>
+        <v>0.125</v>
       </c>
     </row>
     <row r="185">
@@ -7400,7 +7400,7 @@
         <v>1</v>
       </c>
       <c r="D186" s="25" t="n">
-        <v>0.04347826086956522</v>
+        <v>0.04166666666666666</v>
       </c>
     </row>
     <row r="187">
@@ -7448,10 +7448,10 @@
         </is>
       </c>
       <c r="C190" s="8" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D190" s="25" t="n">
-        <v>0.8260869565217391</v>
+        <v>0.8333333333333334</v>
       </c>
     </row>
     <row r="191">
@@ -7464,7 +7464,7 @@
         <v>2</v>
       </c>
       <c r="D191" s="25" t="n">
-        <v>0.08695652173913043</v>
+        <v>0.08333333333333333</v>
       </c>
     </row>
     <row r="192">
@@ -7477,7 +7477,7 @@
         <v>8</v>
       </c>
       <c r="D192" s="25" t="n">
-        <v>0.3478260869565217</v>
+        <v>0.3333333333333333</v>
       </c>
     </row>
     <row r="193">
@@ -7490,7 +7490,7 @@
         <v>5</v>
       </c>
       <c r="D193" s="25" t="n">
-        <v>0.2173913043478261</v>
+        <v>0.2083333333333333</v>
       </c>
     </row>
     <row r="194">
@@ -7516,7 +7516,7 @@
         <v>1</v>
       </c>
       <c r="D195" s="25" t="n">
-        <v>0.04347826086956522</v>
+        <v>0.04166666666666666</v>
       </c>
     </row>
     <row r="196">
@@ -7542,7 +7542,7 @@
         <v>2</v>
       </c>
       <c r="D197" s="25" t="n">
-        <v>0.08695652173913043</v>
+        <v>0.08333333333333333</v>
       </c>
     </row>
     <row r="198">
@@ -7590,10 +7590,10 @@
         </is>
       </c>
       <c r="C201" s="8" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D201" s="25" t="n">
-        <v>0.5652173913043478</v>
+        <v>0.5833333333333334</v>
       </c>
     </row>
     <row r="202">
@@ -7606,7 +7606,7 @@
         <v>8</v>
       </c>
       <c r="D202" s="25" t="n">
-        <v>0.3478260869565217</v>
+        <v>0.3333333333333333</v>
       </c>
     </row>
     <row r="203">
@@ -7619,7 +7619,7 @@
         <v>1</v>
       </c>
       <c r="D203" s="25" t="n">
-        <v>0.04347826086956522</v>
+        <v>0.04166666666666666</v>
       </c>
     </row>
     <row r="204">
@@ -7667,10 +7667,10 @@
         </is>
       </c>
       <c r="C207" s="8" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D207" s="25" t="n">
-        <v>0.7391304347826086</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="208">
@@ -7683,7 +7683,7 @@
         <v>5</v>
       </c>
       <c r="D208" s="25" t="n">
-        <v>0.2173913043478261</v>
+        <v>0.2083333333333333</v>
       </c>
     </row>
     <row r="209">
@@ -7734,7 +7734,7 @@
         <v>2</v>
       </c>
       <c r="D212" s="25" t="n">
-        <v>0.08695652173913043</v>
+        <v>0.08333333333333333</v>
       </c>
     </row>
     <row r="213">
@@ -7747,7 +7747,7 @@
         <v>9</v>
       </c>
       <c r="D213" s="25" t="n">
-        <v>0.391304347826087</v>
+        <v>0.375</v>
       </c>
     </row>
     <row r="214">
@@ -7760,7 +7760,7 @@
         <v>3</v>
       </c>
       <c r="D214" s="25" t="n">
-        <v>0.1304347826086956</v>
+        <v>0.125</v>
       </c>
     </row>
     <row r="215">
@@ -7770,10 +7770,10 @@
         </is>
       </c>
       <c r="C215" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D215" s="25" t="n">
-        <v>0.04347826086956522</v>
+        <v>0.08333333333333333</v>
       </c>
     </row>
     <row r="216">
@@ -7786,7 +7786,7 @@
         <v>2</v>
       </c>
       <c r="D216" s="25" t="n">
-        <v>0.08695652173913043</v>
+        <v>0.08333333333333333</v>
       </c>
     </row>
     <row r="217">
@@ -7837,7 +7837,7 @@
         <v>7</v>
       </c>
       <c r="D220" s="25" t="n">
-        <v>0.3043478260869565</v>
+        <v>0.2916666666666667</v>
       </c>
     </row>
     <row r="221">
@@ -7863,7 +7863,7 @@
         <v>1</v>
       </c>
       <c r="D222" s="25" t="n">
-        <v>0.04347826086956522</v>
+        <v>0.04166666666666666</v>
       </c>
     </row>
     <row r="223">
@@ -7899,10 +7899,10 @@
         </is>
       </c>
       <c r="C225" s="8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D225" s="25" t="n">
-        <v>0.391304347826087</v>
+        <v>0.4166666666666667</v>
       </c>
     </row>
     <row r="226">
@@ -7915,7 +7915,7 @@
         <v>5</v>
       </c>
       <c r="D226" s="25" t="n">
-        <v>0.2173913043478261</v>
+        <v>0.2083333333333333</v>
       </c>
     </row>
     <row r="227">
@@ -7966,7 +7966,7 @@
         <v>7</v>
       </c>
       <c r="D230" s="25" t="n">
-        <v>0.3043478260869565</v>
+        <v>0.2916666666666667</v>
       </c>
     </row>
     <row r="231">
@@ -7979,7 +7979,7 @@
         <v>2</v>
       </c>
       <c r="D231" s="25" t="n">
-        <v>0.08695652173913043</v>
+        <v>0.08333333333333333</v>
       </c>
     </row>
     <row r="232">
@@ -8005,7 +8005,7 @@
         <v>1</v>
       </c>
       <c r="D233" s="25" t="n">
-        <v>0.04347826086956522</v>
+        <v>0.04166666666666666</v>
       </c>
     </row>
     <row r="234">
@@ -8028,10 +8028,10 @@
         </is>
       </c>
       <c r="C235" s="8" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D235" s="25" t="n">
-        <v>0.6956521739130435</v>
+        <v>0.7083333333333334</v>
       </c>
     </row>
     <row r="236">
@@ -8082,7 +8082,7 @@
         <v>4</v>
       </c>
       <c r="D239" s="25" t="n">
-        <v>0.1739130434782609</v>
+        <v>0.1666666666666667</v>
       </c>
     </row>
     <row r="240">
@@ -8095,7 +8095,7 @@
         <v>3</v>
       </c>
       <c r="D240" s="25" t="n">
-        <v>0.1304347826086956</v>
+        <v>0.125</v>
       </c>
     </row>
     <row r="241">
@@ -8178,7 +8178,7 @@
       </c>
       <c r="C247" s="32" t="inlineStr">
         <is>
-          <t>4.7 Years</t>
+          <t>4.5 Years</t>
         </is>
       </c>
     </row>
@@ -8190,7 +8190,7 @@
       </c>
       <c r="C248" s="32" t="inlineStr">
         <is>
-          <t>3.6 Years</t>
+          <t>3.5 Years</t>
         </is>
       </c>
     </row>
